--- a/input/mapping/010. OCB_GOLD_TCKH_V_FTP_003_PHAT.xlsx
+++ b/input/mapping/010. OCB_GOLD_TCKH_V_FTP_003_PHAT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5748" documentId="8_{41A8C51D-6532-4D26-9282-D081DB647141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{624A0BF1-DD28-4246-8BEE-16FB695C0B6B}"/>
+  <xr:revisionPtr revIDLastSave="5745" documentId="8_{41A8C51D-6532-4D26-9282-D081DB647141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F1DB457-98A2-4A95-8829-7419FB513BF4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="838" firstSheet="1" activeTab="8" xr2:uid="{CDFBD334-D065-4A45-A0C3-FE4463186C1A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="838" firstSheet="1" activeTab="1" xr2:uid="{CDFBD334-D065-4A45-A0C3-FE4463186C1A}"/>
   </bookViews>
   <sheets>
     <sheet name="SUMMARY" sheetId="27" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="367">
   <si>
     <t>V_FTP_003  —  Data Lineage Summary</t>
   </si>
@@ -155,9 +155,6 @@
   </si>
   <si>
     <t>Script SQL</t>
-  </si>
-  <si>
-    <t>Code mới</t>
   </si>
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
@@ -282,35 +279,52 @@
 WHERE DATA_DATE = :DATADT;
 INSERT INTO MUABAN_VON_DTL
 WITH
+-- CIF_NAME: SFDB2.IP -&gt; hub_customer + sat_customer_information (ban moi nhat &lt;= DATADT)
 cust AS (
-    SELECT hc.business_key AS CIF,
-           max_by(sci.name_1, sci.source_event_date) AS CIF_NAME
+    SELECT hc.business_key AS CIF, sci.name_1 AS CIF_NAME
     FROM ocb_datavault_pilotcloud_cleaned.raw_vault.hub_customer hc
-    JOIN ocb_datavault_pilotcloud_cleaned.raw_vault.sat_customer_information sci
-      ON sci.customer_hashkey = hc.customer_hashkey
-    WHERE sci.source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
-    GROUP BY hc.business_key
+    JOIN (
+        SELECT customer_hashkey, name_1,
+               ROW_NUMBER() OVER (PARTITION BY customer_hashkey
+                                  ORDER BY source_event_date DESC) rn
+        FROM ocb_datavault_pilotcloud_cleaned.raw_vault.sat_customer_information
+        WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    ) sci ON sci.customer_hashkey = hc.customer_hashkey AND sci.rn = 1
 ),
+-- PRODUCT_NAME: SFDB2.PD (COMB_APPPRODUCT) -&gt; sat_app_product
+-- Join productcode = c.PRODUCT (KHONG dung hub.business_key vi hub keyed by id).
 prod AS (
-    SELECT productcode AS PRODUCT_CODE,
-           max_by(productname, source_event_date) AS PRODUCT_NAME
-    FROM ocb_datavault_pilotcloud_cleaned.raw_vault.sat_app_product
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
-    GROUP BY productcode
+    SELECT productcode AS PRODUCT_CODE, productname AS PRODUCT_NAME
+    FROM (
+        SELECT productcode, productname,
+               ROW_NUMBER() OVER (PARTITION BY productcode
+                                  ORDER BY source_event_date DESC) rn
+        FROM ocb_datavault_pilotcloud_cleaned.raw_vault.sat_app_product
+        WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    ) x WHERE rn = 1
 ),
+-- CATEG_NAME: T24_CATEGORY -&gt; ref_t24_category (Ref_code = c.CATEGORY)
+-- SOR dung T_SHORT_NAME (KHONG phai T_DESCRIPTION).
 categ AS (
-    SELECT Ref_code AS CATEG_CODE,
-           max_by(T_SHORT_NAME, source_event_date) AS CATEG_NAME
-    FROM ocb_datavault_pilotcloud_cleaned.raw_vault.ref_t24_category
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
-    GROUP BY Ref_code
+    SELECT Ref_code AS CATEG_CODE, T_SHORT_NAME AS CATEG_NAME
+    FROM (
+        SELECT Ref_code, T_SHORT_NAME,
+               ROW_NUMBER() OVER (PARTITION BY Ref_code
+                                  ORDER BY source_event_date DESC) rn
+        FROM ocb_datavault_pilotcloud_cleaned.raw_vault.ref_t24_category
+        WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    ) x WHERE rn = 1
 ),
+-- PROMOTION_NAME: T24_LD_PROMOTION -&gt; ref_t24_ld_promotion (Ref_code = c.PROMOTION_ID)
 promo AS (
-    SELECT Ref_code AS PROMO_CODE,
-           max_by(Ref_description, source_event_date) AS PROMO_NAME
-    FROM ocb_datavault_pilotcloud_cleaned.raw_vault.ref_t24_ld_promotion
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
-    GROUP BY Ref_code
+    SELECT Ref_code AS PROMO_CODE, Ref_description AS PROMO_NAME
+    FROM (
+        SELECT Ref_code, Ref_description,
+               ROW_NUMBER() OVER (PARTITION BY Ref_code
+                                  ORDER BY source_event_date DESC) rn
+        FROM ocb_datavault_pilotcloud_cleaned.raw_vault.ref_t24_ld_promotion
+        WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    ) x WHERE rn = 1
 )
 SELECT
     c.DATA_DATE                                                       AS DATA_DATE,
@@ -321,7 +335,7 @@
     c.SYSTEM_ID                                                       AS SYSTEM_ID,
     c.CUSTGROUP                                                       AS CUST_GROUP,
     CAST(c.CIF AS STRING)                                             AS CIF,
-    cust.CIF_NAME                                                     AS CIF_NAME,         
+    cust.CIF_NAME                                                     AS CIF_NAME,         -- [S3]
     CASE WHEN c.PRODUCT IN (SELECT PARA_VALUE FROM FTP_PARAM
                             WHERE PARA_NAME = 'FTP_FLEXI_SAVING')
          THEN c.AR_NO ELSE c.REF_NO END                              AS CONTRACT_NO,
@@ -347,7 +361,7 @@
     a.DEBIT_ACCOUNT_BR                                                AS TK_NO,
     a.CREDIT_ACCOUNT_BR                                               AS TK_CO,
     CAST(c.INT_RT AS DECIMAL(15,4))                                   AS T24_INRATE,
-    CAST(c.GL_ACCOUNT AS DECIMAL(18,0))                               AS GL,             
+    CAST(c.GL_ACCOUNT AS DECIMAL(18,0))                               AS GL,             -- StringToDecimal
     CAST(c.CATEGORY AS DECIMAL(10,0))                                 AS CATEG,
     categ.CATEG_NAME                                                  AS CATEG_NAME,
     c.PRODUCT                                                         AS PRODUCT_ID,
@@ -358,7 +372,7 @@
                 OR c.DATE_END_RECAL &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
               THEN c.TOTAL_INT_RATE
               ELSE c.FTP_BEFORE_RECAL_RATE END AS DECIMAL(20,4))      AS TONG_LSDCV_TRUOC_UUDAI_LS,
-    c.DATE_END_RECAL                                                  AS END_DATE_FROM,   
+    c.DATE_END_RECAL                                                  AS END_DATE_FROM,   -- [S5]
     c.CONTRACT_TYPE                                                   AS CONTRACT_TYPE
 FROM FTP_CONTRACT_HIST c
 LEFT JOIN FTP_ACCRUAL a
@@ -2838,18 +2852,63 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2868,51 +2927,6 @@
     <xf numFmtId="0" fontId="30" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2979,6 +2993,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2988,12 +3008,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3042,8 +3056,8 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3053,8 +3067,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFE67E22"/>
       <color rgb="FF00B050"/>
-      <color rgb="FFE67E22"/>
       <color rgb="FFA5A5A5"/>
       <color rgb="FFFEF3E2"/>
     </mruColors>
@@ -3462,51 +3476,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="19.5">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="127"/>
-      <c r="R1" s="127"/>
-      <c r="S1" s="127"/>
-      <c r="T1" s="127"/>
-      <c r="U1" s="127"/>
-      <c r="V1" s="127"/>
-      <c r="W1" s="127"/>
-      <c r="X1" s="128"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="120"/>
     </row>
     <row r="2" spans="1:24" ht="25.5" customHeight="1">
       <c r="A2" s="73"/>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="133" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="E2" s="116" t="s">
+      <c r="C2" s="133"/>
+      <c r="E2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="116"/>
-      <c r="H2" s="117" t="s">
+      <c r="F2" s="133"/>
+      <c r="H2" s="134" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="117"/>
-      <c r="K2" s="117" t="s">
+      <c r="I2" s="134"/>
+      <c r="K2" s="134" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="117"/>
+      <c r="L2" s="134"/>
       <c r="N2" s="74"/>
       <c r="O2" s="74"/>
       <c r="Q2" s="74"/>
@@ -3514,152 +3528,152 @@
     </row>
     <row r="3" spans="1:24" ht="15" customHeight="1">
       <c r="A3" s="73"/>
-      <c r="B3" s="140" t="s">
+      <c r="B3" s="132" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="140"/>
-      <c r="D3" s="118" t="s">
+      <c r="C3" s="132"/>
+      <c r="D3" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="129" t="s">
+      <c r="E3" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="129"/>
-      <c r="G3" s="118" t="s">
+      <c r="F3" s="121"/>
+      <c r="G3" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="119" t="s">
+      <c r="H3" s="116" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="119"/>
-      <c r="J3" s="118" t="s">
+      <c r="I3" s="116"/>
+      <c r="J3" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="130" t="s">
+      <c r="K3" s="122" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="130"/>
+      <c r="L3" s="122"/>
       <c r="M3" s="75"/>
     </row>
     <row r="4" spans="1:24" ht="15" customHeight="1">
       <c r="A4" s="76"/>
-      <c r="B4" s="140"/>
-      <c r="C4" s="140"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="130"/>
-      <c r="L4" s="130"/>
+      <c r="B4" s="132"/>
+      <c r="C4" s="132"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
       <c r="M4" s="75"/>
     </row>
     <row r="5" spans="1:24" ht="15" customHeight="1">
       <c r="A5" s="76"/>
-      <c r="B5" s="140"/>
-      <c r="C5" s="140"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="129"/>
-      <c r="F5" s="129"/>
-      <c r="K5" s="130"/>
-      <c r="L5" s="130"/>
+      <c r="B5" s="132"/>
+      <c r="C5" s="132"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="121"/>
+      <c r="F5" s="121"/>
+      <c r="K5" s="122"/>
+      <c r="L5" s="122"/>
       <c r="N5" s="77"/>
       <c r="O5" s="77"/>
     </row>
     <row r="6" spans="1:24" ht="15" customHeight="1">
       <c r="A6" s="76"/>
-      <c r="B6" s="140"/>
-      <c r="C6" s="140"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="129"/>
-      <c r="F6" s="129"/>
-      <c r="G6" s="118" t="s">
+      <c r="B6" s="132"/>
+      <c r="C6" s="132"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="119" t="s">
+      <c r="H6" s="116" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="119"/>
-      <c r="J6" s="118" t="s">
+      <c r="I6" s="116"/>
+      <c r="J6" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="130"/>
-      <c r="L6" s="130"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="122"/>
       <c r="M6" s="75"/>
     </row>
     <row r="7" spans="1:24" ht="15" customHeight="1">
       <c r="A7" s="76"/>
-      <c r="B7" s="140"/>
-      <c r="C7" s="140"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="129"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="119"/>
-      <c r="I7" s="119"/>
-      <c r="J7" s="118"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="130"/>
+      <c r="B7" s="132"/>
+      <c r="C7" s="132"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="121"/>
+      <c r="F7" s="121"/>
+      <c r="G7" s="117"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
+      <c r="K7" s="122"/>
+      <c r="L7" s="122"/>
       <c r="M7" s="75"/>
     </row>
     <row r="8" spans="1:24" ht="15" customHeight="1">
       <c r="A8" s="76"/>
-      <c r="B8" s="140"/>
-      <c r="C8" s="140"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="129"/>
-      <c r="F8" s="129"/>
+      <c r="B8" s="132"/>
+      <c r="C8" s="132"/>
+      <c r="D8" s="117"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
     </row>
     <row r="9" spans="1:24" ht="15" customHeight="1">
       <c r="A9" s="76"/>
-      <c r="B9" s="140"/>
-      <c r="C9" s="140"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="129"/>
-      <c r="F9" s="129"/>
-      <c r="G9" s="118" t="s">
+      <c r="B9" s="132"/>
+      <c r="C9" s="132"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="120" t="s">
+      <c r="H9" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="121"/>
-      <c r="J9" s="118" t="s">
+      <c r="I9" s="136"/>
+      <c r="J9" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="K9" s="119" t="s">
+      <c r="K9" s="184" t="s">
         <v>12</v>
       </c>
-      <c r="L9" s="119"/>
-      <c r="M9" s="118" t="s">
+      <c r="L9" s="184"/>
+      <c r="M9" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="N9" s="119" t="s">
+      <c r="N9" s="184" t="s">
         <v>13</v>
       </c>
-      <c r="O9" s="119"/>
+      <c r="O9" s="184"/>
       <c r="Q9" s="81" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="15" customHeight="1">
       <c r="A10" s="76"/>
-      <c r="B10" s="140"/>
-      <c r="C10" s="140"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="118"/>
-      <c r="H10" s="122"/>
-      <c r="I10" s="123"/>
-      <c r="J10" s="118"/>
-      <c r="K10" s="119"/>
-      <c r="L10" s="119"/>
-      <c r="M10" s="118"/>
-      <c r="N10" s="119"/>
-      <c r="O10" s="119"/>
+      <c r="B10" s="132"/>
+      <c r="C10" s="132"/>
+      <c r="D10" s="117"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="117"/>
+      <c r="H10" s="137"/>
+      <c r="I10" s="138"/>
+      <c r="J10" s="117"/>
+      <c r="K10" s="184"/>
+      <c r="L10" s="184"/>
+      <c r="M10" s="117"/>
+      <c r="N10" s="184"/>
+      <c r="O10" s="184"/>
       <c r="Q10" s="82"/>
       <c r="R10" s="83" t="s">
         <v>15</v>
@@ -3667,14 +3681,14 @@
     </row>
     <row r="11" spans="1:24" ht="15" customHeight="1">
       <c r="A11" s="76"/>
-      <c r="B11" s="140"/>
-      <c r="C11" s="140"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="129"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="118"/>
-      <c r="H11" s="122"/>
-      <c r="I11" s="123"/>
+      <c r="B11" s="132"/>
+      <c r="C11" s="132"/>
+      <c r="D11" s="117"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="117"/>
+      <c r="H11" s="137"/>
+      <c r="I11" s="138"/>
       <c r="J11" s="75"/>
       <c r="M11" s="75"/>
       <c r="N11" s="77"/>
@@ -3685,21 +3699,21 @@
       </c>
     </row>
     <row r="12" spans="1:24" ht="15" customHeight="1">
-      <c r="B12" s="140"/>
-      <c r="C12" s="140"/>
-      <c r="D12" s="118"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="129"/>
-      <c r="G12" s="118"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="123"/>
-      <c r="J12" s="118" t="s">
+      <c r="B12" s="132"/>
+      <c r="C12" s="132"/>
+      <c r="D12" s="117"/>
+      <c r="E12" s="121"/>
+      <c r="F12" s="121"/>
+      <c r="G12" s="117"/>
+      <c r="H12" s="137"/>
+      <c r="I12" s="138"/>
+      <c r="J12" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="K12" s="119" t="s">
+      <c r="K12" s="184" t="s">
         <v>17</v>
       </c>
-      <c r="L12" s="119"/>
+      <c r="L12" s="184"/>
       <c r="M12" s="75"/>
       <c r="N12" s="78"/>
       <c r="O12" s="78"/>
@@ -3709,17 +3723,17 @@
       </c>
     </row>
     <row r="13" spans="1:24" ht="15" customHeight="1">
-      <c r="B13" s="140"/>
-      <c r="C13" s="140"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="129"/>
-      <c r="F13" s="129"/>
-      <c r="G13" s="118"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="123"/>
-      <c r="J13" s="118"/>
-      <c r="K13" s="119"/>
-      <c r="L13" s="119"/>
+      <c r="B13" s="132"/>
+      <c r="C13" s="132"/>
+      <c r="D13" s="117"/>
+      <c r="E13" s="121"/>
+      <c r="F13" s="121"/>
+      <c r="G13" s="117"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="138"/>
+      <c r="J13" s="117"/>
+      <c r="K13" s="184"/>
+      <c r="L13" s="184"/>
       <c r="M13" s="75"/>
       <c r="N13" s="78"/>
       <c r="O13" s="79"/>
@@ -3729,14 +3743,14 @@
       </c>
     </row>
     <row r="14" spans="1:24" ht="15" customHeight="1">
-      <c r="B14" s="140"/>
-      <c r="C14" s="140"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="129"/>
-      <c r="F14" s="129"/>
-      <c r="G14" s="118"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="123"/>
+      <c r="B14" s="132"/>
+      <c r="C14" s="132"/>
+      <c r="D14" s="117"/>
+      <c r="E14" s="121"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="117"/>
+      <c r="H14" s="137"/>
+      <c r="I14" s="138"/>
       <c r="N14" s="78"/>
       <c r="O14" s="78"/>
       <c r="Q14" s="87"/>
@@ -3745,67 +3759,67 @@
       </c>
     </row>
     <row r="15" spans="1:24" ht="15" customHeight="1">
-      <c r="B15" s="140"/>
-      <c r="C15" s="140"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="129"/>
-      <c r="G15" s="118"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="123"/>
-      <c r="J15" s="118" t="s">
+      <c r="B15" s="132"/>
+      <c r="C15" s="132"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="121"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="137"/>
+      <c r="I15" s="138"/>
+      <c r="J15" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="K15" s="119" t="s">
+      <c r="K15" s="184" t="s">
         <v>21</v>
       </c>
-      <c r="L15" s="119"/>
+      <c r="L15" s="184"/>
       <c r="N15" s="80"/>
       <c r="O15" s="79"/>
     </row>
     <row r="16" spans="1:24" ht="15" customHeight="1">
-      <c r="B16" s="140"/>
-      <c r="C16" s="140"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="129"/>
-      <c r="F16" s="129"/>
-      <c r="G16" s="118"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="123"/>
-      <c r="J16" s="118"/>
-      <c r="K16" s="119"/>
-      <c r="L16" s="119"/>
+      <c r="B16" s="132"/>
+      <c r="C16" s="132"/>
+      <c r="D16" s="117"/>
+      <c r="E16" s="121"/>
+      <c r="F16" s="121"/>
+      <c r="G16" s="117"/>
+      <c r="H16" s="137"/>
+      <c r="I16" s="138"/>
+      <c r="J16" s="117"/>
+      <c r="K16" s="184"/>
+      <c r="L16" s="184"/>
       <c r="N16" s="78"/>
       <c r="O16" s="78"/>
     </row>
     <row r="17" spans="2:19" ht="15" customHeight="1">
-      <c r="B17" s="140"/>
-      <c r="C17" s="140"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="129"/>
-      <c r="F17" s="129"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="123"/>
+      <c r="B17" s="132"/>
+      <c r="C17" s="132"/>
+      <c r="D17" s="117"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="117"/>
+      <c r="H17" s="137"/>
+      <c r="I17" s="138"/>
       <c r="N17" s="80"/>
       <c r="O17" s="79"/>
     </row>
     <row r="18" spans="2:19" ht="15" customHeight="1">
-      <c r="B18" s="140"/>
-      <c r="C18" s="140"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="129"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="123"/>
-      <c r="J18" s="118" t="s">
+      <c r="B18" s="132"/>
+      <c r="C18" s="132"/>
+      <c r="D18" s="117"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="121"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="137"/>
+      <c r="I18" s="138"/>
+      <c r="J18" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="K18" s="119" t="s">
+      <c r="K18" s="184" t="s">
         <v>22</v>
       </c>
-      <c r="L18" s="119"/>
+      <c r="L18" s="184"/>
       <c r="N18" s="78"/>
       <c r="O18" s="78"/>
       <c r="Q18" s="88" t="s">
@@ -3819,17 +3833,17 @@
       </c>
     </row>
     <row r="19" spans="2:19" ht="18" customHeight="1">
-      <c r="B19" s="140"/>
-      <c r="C19" s="140"/>
-      <c r="D19" s="118"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="129"/>
-      <c r="G19" s="118"/>
-      <c r="H19" s="122"/>
-      <c r="I19" s="123"/>
-      <c r="J19" s="118"/>
-      <c r="K19" s="119"/>
-      <c r="L19" s="119"/>
+      <c r="B19" s="132"/>
+      <c r="C19" s="132"/>
+      <c r="D19" s="117"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="117"/>
+      <c r="H19" s="137"/>
+      <c r="I19" s="138"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="184"/>
+      <c r="L19" s="184"/>
       <c r="N19" s="80"/>
       <c r="O19" s="79"/>
       <c r="Q19" s="90" t="s">
@@ -3843,14 +3857,14 @@
       </c>
     </row>
     <row r="20" spans="2:19" ht="15" customHeight="1">
-      <c r="B20" s="140"/>
-      <c r="C20" s="140"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="129"/>
-      <c r="F20" s="129"/>
-      <c r="G20" s="118"/>
-      <c r="H20" s="122"/>
-      <c r="I20" s="123"/>
+      <c r="B20" s="132"/>
+      <c r="C20" s="132"/>
+      <c r="D20" s="117"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="121"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="137"/>
+      <c r="I20" s="138"/>
       <c r="N20" s="78"/>
       <c r="O20" s="78"/>
       <c r="Q20" s="90" t="s">
@@ -3864,21 +3878,21 @@
       </c>
     </row>
     <row r="21" spans="2:19" ht="15" customHeight="1">
-      <c r="B21" s="140"/>
-      <c r="C21" s="140"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="129"/>
-      <c r="F21" s="129"/>
-      <c r="G21" s="118"/>
-      <c r="H21" s="122"/>
-      <c r="I21" s="123"/>
-      <c r="J21" s="137" t="s">
+      <c r="B21" s="132"/>
+      <c r="C21" s="132"/>
+      <c r="D21" s="117"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="121"/>
+      <c r="G21" s="117"/>
+      <c r="H21" s="137"/>
+      <c r="I21" s="138"/>
+      <c r="J21" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="K21" s="131" t="s">
+      <c r="K21" s="123" t="s">
         <v>27</v>
       </c>
-      <c r="L21" s="132"/>
+      <c r="L21" s="124"/>
       <c r="N21" s="80"/>
       <c r="O21" s="79"/>
       <c r="Q21" s="90" t="s">
@@ -3892,17 +3906,17 @@
       </c>
     </row>
     <row r="22" spans="2:19" ht="15" customHeight="1">
-      <c r="B22" s="140"/>
-      <c r="C22" s="140"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="129"/>
-      <c r="F22" s="129"/>
-      <c r="G22" s="118"/>
-      <c r="H22" s="122"/>
-      <c r="I22" s="123"/>
-      <c r="J22" s="138"/>
-      <c r="K22" s="133"/>
-      <c r="L22" s="134"/>
+      <c r="B22" s="132"/>
+      <c r="C22" s="132"/>
+      <c r="D22" s="117"/>
+      <c r="E22" s="121"/>
+      <c r="F22" s="121"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="137"/>
+      <c r="I22" s="138"/>
+      <c r="J22" s="130"/>
+      <c r="K22" s="125"/>
+      <c r="L22" s="126"/>
       <c r="N22" s="78"/>
       <c r="O22" s="78"/>
       <c r="Q22" s="90" t="s">
@@ -3916,17 +3930,17 @@
       </c>
     </row>
     <row r="23" spans="2:19" ht="14.25" customHeight="1">
-      <c r="B23" s="140"/>
-      <c r="C23" s="140"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="129"/>
-      <c r="F23" s="129"/>
-      <c r="G23" s="118"/>
-      <c r="H23" s="122"/>
-      <c r="I23" s="123"/>
-      <c r="J23" s="138"/>
-      <c r="K23" s="133"/>
-      <c r="L23" s="134"/>
+      <c r="B23" s="132"/>
+      <c r="C23" s="132"/>
+      <c r="D23" s="117"/>
+      <c r="E23" s="121"/>
+      <c r="F23" s="121"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="137"/>
+      <c r="I23" s="138"/>
+      <c r="J23" s="130"/>
+      <c r="K23" s="125"/>
+      <c r="L23" s="126"/>
       <c r="N23" s="80"/>
       <c r="O23" s="78"/>
       <c r="Q23" s="99" t="s">
@@ -3940,17 +3954,17 @@
       </c>
     </row>
     <row r="24" spans="2:19" ht="15" customHeight="1">
-      <c r="B24" s="140"/>
-      <c r="C24" s="140"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="129"/>
-      <c r="F24" s="129"/>
-      <c r="G24" s="118"/>
-      <c r="H24" s="122"/>
-      <c r="I24" s="123"/>
-      <c r="J24" s="138"/>
-      <c r="K24" s="133"/>
-      <c r="L24" s="134"/>
+      <c r="B24" s="132"/>
+      <c r="C24" s="132"/>
+      <c r="D24" s="117"/>
+      <c r="E24" s="121"/>
+      <c r="F24" s="121"/>
+      <c r="G24" s="117"/>
+      <c r="H24" s="137"/>
+      <c r="I24" s="138"/>
+      <c r="J24" s="130"/>
+      <c r="K24" s="125"/>
+      <c r="L24" s="126"/>
       <c r="N24" s="78"/>
       <c r="O24" s="93"/>
       <c r="Q24" s="100" t="s">
@@ -3964,17 +3978,17 @@
       </c>
     </row>
     <row r="25" spans="2:19" ht="15" customHeight="1">
-      <c r="B25" s="140"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="118"/>
-      <c r="E25" s="129"/>
-      <c r="F25" s="129"/>
-      <c r="G25" s="118"/>
-      <c r="H25" s="122"/>
-      <c r="I25" s="123"/>
-      <c r="J25" s="139"/>
-      <c r="K25" s="135"/>
-      <c r="L25" s="136"/>
+      <c r="B25" s="132"/>
+      <c r="C25" s="132"/>
+      <c r="D25" s="117"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="121"/>
+      <c r="G25" s="117"/>
+      <c r="H25" s="137"/>
+      <c r="I25" s="138"/>
+      <c r="J25" s="131"/>
+      <c r="K25" s="127"/>
+      <c r="L25" s="128"/>
       <c r="N25" s="80"/>
       <c r="O25" s="93"/>
       <c r="Q25" s="100" t="s">
@@ -3988,14 +4002,14 @@
       </c>
     </row>
     <row r="26" spans="2:19" ht="15" customHeight="1">
-      <c r="B26" s="140"/>
-      <c r="C26" s="140"/>
-      <c r="D26" s="118"/>
-      <c r="E26" s="129"/>
-      <c r="F26" s="129"/>
-      <c r="G26" s="118"/>
-      <c r="H26" s="122"/>
-      <c r="I26" s="123"/>
+      <c r="B26" s="132"/>
+      <c r="C26" s="132"/>
+      <c r="D26" s="117"/>
+      <c r="E26" s="121"/>
+      <c r="F26" s="121"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="137"/>
+      <c r="I26" s="138"/>
       <c r="N26" s="78"/>
       <c r="O26" s="93"/>
       <c r="Q26" s="100" t="s">
@@ -4009,66 +4023,81 @@
       </c>
     </row>
     <row r="27" spans="2:19" ht="15" customHeight="1">
-      <c r="B27" s="140"/>
-      <c r="C27" s="140"/>
-      <c r="D27" s="118"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="129"/>
-      <c r="G27" s="118"/>
-      <c r="H27" s="122"/>
-      <c r="I27" s="123"/>
-      <c r="J27" s="137" t="s">
+      <c r="B27" s="132"/>
+      <c r="C27" s="132"/>
+      <c r="D27" s="117"/>
+      <c r="E27" s="121"/>
+      <c r="F27" s="121"/>
+      <c r="G27" s="117"/>
+      <c r="H27" s="137"/>
+      <c r="I27" s="138"/>
+      <c r="J27" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="K27" s="131" t="s">
+      <c r="K27" s="123" t="s">
         <v>29</v>
       </c>
-      <c r="L27" s="132"/>
+      <c r="L27" s="124"/>
       <c r="P27" s="96"/>
       <c r="Q27" s="96"/>
       <c r="R27" s="96"/>
     </row>
     <row r="28" spans="2:19" ht="15" customHeight="1">
-      <c r="B28" s="140"/>
-      <c r="C28" s="140"/>
-      <c r="D28" s="118"/>
-      <c r="E28" s="129"/>
-      <c r="F28" s="129"/>
-      <c r="G28" s="118"/>
-      <c r="H28" s="122"/>
-      <c r="I28" s="123"/>
-      <c r="J28" s="138"/>
-      <c r="K28" s="133"/>
-      <c r="L28" s="134"/>
+      <c r="B28" s="132"/>
+      <c r="C28" s="132"/>
+      <c r="D28" s="117"/>
+      <c r="E28" s="121"/>
+      <c r="F28" s="121"/>
+      <c r="G28" s="117"/>
+      <c r="H28" s="137"/>
+      <c r="I28" s="138"/>
+      <c r="J28" s="130"/>
+      <c r="K28" s="125"/>
+      <c r="L28" s="126"/>
     </row>
     <row r="29" spans="2:19" ht="15" customHeight="1">
-      <c r="B29" s="140"/>
-      <c r="C29" s="140"/>
-      <c r="D29" s="118"/>
-      <c r="E29" s="129"/>
-      <c r="F29" s="129"/>
-      <c r="G29" s="118"/>
-      <c r="H29" s="122"/>
-      <c r="I29" s="123"/>
-      <c r="J29" s="138"/>
-      <c r="K29" s="133"/>
-      <c r="L29" s="134"/>
+      <c r="B29" s="132"/>
+      <c r="C29" s="132"/>
+      <c r="D29" s="117"/>
+      <c r="E29" s="121"/>
+      <c r="F29" s="121"/>
+      <c r="G29" s="117"/>
+      <c r="H29" s="137"/>
+      <c r="I29" s="138"/>
+      <c r="J29" s="130"/>
+      <c r="K29" s="125"/>
+      <c r="L29" s="126"/>
     </row>
     <row r="30" spans="2:19" ht="21.75" customHeight="1">
-      <c r="B30" s="140"/>
-      <c r="C30" s="140"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="129"/>
-      <c r="F30" s="129"/>
-      <c r="G30" s="118"/>
-      <c r="H30" s="124"/>
-      <c r="I30" s="125"/>
-      <c r="J30" s="139"/>
-      <c r="K30" s="135"/>
-      <c r="L30" s="136"/>
+      <c r="B30" s="132"/>
+      <c r="C30" s="132"/>
+      <c r="D30" s="117"/>
+      <c r="E30" s="121"/>
+      <c r="F30" s="121"/>
+      <c r="G30" s="117"/>
+      <c r="H30" s="139"/>
+      <c r="I30" s="140"/>
+      <c r="J30" s="131"/>
+      <c r="K30" s="127"/>
+      <c r="L30" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="D3:D30"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H3:I4"/>
+    <mergeCell ref="H6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="H9:I30"/>
     <mergeCell ref="N9:O10"/>
     <mergeCell ref="M9:M10"/>
     <mergeCell ref="A1:X1"/>
@@ -4085,21 +4114,6 @@
     <mergeCell ref="J27:J30"/>
     <mergeCell ref="B3:C30"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="D3:D30"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H3:I4"/>
-    <mergeCell ref="H6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="H9:I30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4125,7 +4139,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="45" customHeight="1">
       <c r="A1" s="176" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B1" s="177"/>
       <c r="C1" s="177"/>
@@ -4135,20 +4149,20 @@
     </row>
     <row r="2" spans="1:6" ht="18.75">
       <c r="A2" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="51" t="s">
+      <c r="C2" s="178" t="s">
         <v>43</v>
-      </c>
-      <c r="C2" s="178" t="s">
-        <v>44</v>
       </c>
       <c r="D2" s="178"/>
       <c r="E2" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>45</v>
-      </c>
-      <c r="F2" s="51" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="32.25" customHeight="1">
@@ -4169,7 +4183,7 @@
     </row>
     <row r="5" spans="1:6" ht="18.75">
       <c r="A5" s="178" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B5" s="178"/>
       <c r="C5" s="178"/>
@@ -4182,88 +4196,88 @@
         <v>31</v>
       </c>
       <c r="B6" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="51" t="s">
-        <v>154</v>
-      </c>
-      <c r="D6" s="51" t="s">
+      <c r="E6" s="51" t="s">
         <v>55</v>
-      </c>
-      <c r="E6" s="51" t="s">
-        <v>56</v>
       </c>
       <c r="F6" s="46"/>
     </row>
     <row r="7" spans="1:6" ht="18.75">
       <c r="A7" s="52" t="s">
+        <v>353</v>
+      </c>
+      <c r="B7" s="48" t="s">
         <v>354</v>
       </c>
-      <c r="B7" s="48" t="s">
-        <v>355</v>
-      </c>
       <c r="C7" s="48" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" s="48" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F7" s="47"/>
     </row>
     <row r="8" spans="1:6" ht="18.75">
       <c r="A8" s="52" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C8" s="48" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" s="48" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F8" s="47"/>
     </row>
     <row r="9" spans="1:6" ht="18.75">
       <c r="A9" s="52" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C9" s="48" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" s="48" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F9" s="47"/>
     </row>
     <row r="10" spans="1:6" ht="18.75">
       <c r="A10" s="52" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C10" s="48" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" s="48" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F10" s="47"/>
     </row>
@@ -4559,7 +4573,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1">
       <c r="A1" s="181" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B1" s="182"/>
       <c r="C1" s="182"/>
@@ -4569,20 +4583,20 @@
     </row>
     <row r="2" spans="1:6" ht="18.75">
       <c r="A2" s="58" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="C2" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="D2" s="179" t="s">
         <v>44</v>
-      </c>
-      <c r="D2" s="179" t="s">
-        <v>45</v>
       </c>
       <c r="E2" s="179"/>
       <c r="F2" s="58" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="16.5" customHeight="1">
@@ -4603,7 +4617,7 @@
     </row>
     <row r="5" spans="1:6" ht="23.25" customHeight="1">
       <c r="A5" s="179" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B5" s="179"/>
       <c r="C5" s="179"/>
@@ -4616,16 +4630,16 @@
         <v>31</v>
       </c>
       <c r="B6" s="65" t="s">
+        <v>359</v>
+      </c>
+      <c r="C6" s="65" t="s">
         <v>360</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="D6" s="65" t="s">
         <v>361</v>
       </c>
-      <c r="D6" s="65" t="s">
-        <v>362</v>
-      </c>
       <c r="E6" s="65" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F6" s="64"/>
     </row>
@@ -4634,16 +4648,16 @@
         <v>21</v>
       </c>
       <c r="B7" s="66" t="s">
+        <v>362</v>
+      </c>
+      <c r="C7" s="57" t="s">
         <v>363</v>
       </c>
-      <c r="C7" s="57" t="s">
-        <v>364</v>
-      </c>
       <c r="D7" s="67" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" s="66" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F7" s="64"/>
     </row>
@@ -4652,16 +4666,16 @@
         <v>21</v>
       </c>
       <c r="B8" s="66" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8" s="57" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D8" s="67" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" s="66" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F8" s="64"/>
     </row>
@@ -4670,16 +4684,16 @@
         <v>21</v>
       </c>
       <c r="B9" s="66" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D9" s="67" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" s="66" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F9" s="64"/>
     </row>
@@ -4688,16 +4702,16 @@
         <v>21</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C10" s="57" t="s">
+        <v>364</v>
+      </c>
+      <c r="D10" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="66" t="s">
         <v>365</v>
-      </c>
-      <c r="D10" s="67" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="66" t="s">
-        <v>366</v>
       </c>
       <c r="F10" s="64"/>
     </row>
@@ -4706,16 +4720,16 @@
         <v>21</v>
       </c>
       <c r="B11" s="66" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D11" s="67" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E11" s="66" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F11" s="64"/>
     </row>
@@ -4736,7 +4750,6 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.140625" customWidth="1"/>
     <col min="2" max="2" width="33.7109375" customWidth="1"/>
     <col min="3" max="3" width="135.85546875" customWidth="1"/>
   </cols>
@@ -4753,80 +4766,61 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="70" t="s">
-        <v>33</v>
-      </c>
+      <c r="A2" s="70"/>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="71" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="70" t="s">
-        <v>33</v>
-      </c>
+      <c r="A3" s="70"/>
       <c r="B3" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="70" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.899999999999999" customHeight="1">
-      <c r="A4" s="70" t="s">
-        <v>33</v>
-      </c>
       <c r="B4" s="101" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="71" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16.899999999999999" customHeight="1">
-      <c r="A5" s="70" t="s">
-        <v>33</v>
-      </c>
       <c r="B5" s="101" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="184" t="s">
+      <c r="C5" s="71" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="B6" s="101" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="71" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="101" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="71" t="s">
-        <v>38</v>
-      </c>
-    </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="70" t="s">
-        <v>33</v>
-      </c>
       <c r="B7" s="101" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="71" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="70" t="s">
-        <v>33</v>
-      </c>
       <c r="B8" s="101" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="71" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4862,7 +4856,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="51.6" customHeight="1">
       <c r="A1" s="141" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B1" s="142"/>
       <c r="C1" s="142"/>
@@ -4871,19 +4865,19 @@
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C2" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="42" customHeight="1">
@@ -4894,10 +4888,10 @@
         <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -4906,22 +4900,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="40.15" customHeight="1"/>
     <row r="6" spans="1:5" ht="40.15" customHeight="1">
       <c r="A6" s="144" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="145"/>
       <c r="C6" s="145"/>
@@ -4933,43 +4927,43 @@
         <v>31</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="12" t="s">
         <v>55</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>56</v>
       </c>
       <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:5" ht="40.15" customHeight="1">
       <c r="A8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="C8" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>59</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>60</v>
       </c>
       <c r="E8" s="11"/>
     </row>
     <row r="9" spans="1:5" ht="51.6" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="13" t="s">
         <v>61</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>62</v>
       </c>
       <c r="E9" s="11"/>
     </row>
@@ -4978,13 +4972,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="13" t="s">
         <v>63</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>64</v>
       </c>
       <c r="E10" s="11"/>
     </row>
@@ -4993,13 +4987,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="13" t="s">
         <v>65</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>66</v>
       </c>
       <c r="E11" s="11"/>
     </row>
@@ -5008,13 +5002,13 @@
         <v>7</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="13" t="s">
         <v>67</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>68</v>
       </c>
       <c r="E12" s="11"/>
     </row>
@@ -5023,13 +5017,13 @@
         <v>7</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="13" t="s">
         <v>69</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>70</v>
       </c>
       <c r="E13" s="11"/>
     </row>
@@ -5038,13 +5032,13 @@
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>71</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>72</v>
       </c>
       <c r="E14" s="11"/>
     </row>
@@ -5053,13 +5047,13 @@
         <v>7</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>73</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>74</v>
       </c>
       <c r="E15" s="11"/>
     </row>
@@ -5068,13 +5062,13 @@
         <v>7</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>75</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>76</v>
       </c>
       <c r="E16" s="11"/>
     </row>
@@ -5083,13 +5077,13 @@
         <v>7</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="13" t="s">
         <v>77</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>78</v>
       </c>
       <c r="E17" s="11"/>
     </row>
@@ -5098,13 +5092,13 @@
         <v>7</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="D18" s="13" t="s">
         <v>80</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>81</v>
       </c>
       <c r="E18" s="11"/>
     </row>
@@ -5113,13 +5107,13 @@
         <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="13" t="s">
         <v>82</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>83</v>
       </c>
       <c r="E19" s="11"/>
     </row>
@@ -5128,13 +5122,13 @@
         <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="13" t="s">
         <v>84</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>85</v>
       </c>
       <c r="E20" s="11"/>
     </row>
@@ -5143,13 +5137,13 @@
         <v>7</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="13" t="s">
         <v>86</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>87</v>
       </c>
       <c r="E21" s="11"/>
     </row>
@@ -5158,13 +5152,13 @@
         <v>7</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="13" t="s">
         <v>88</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>89</v>
       </c>
       <c r="E22" s="11"/>
     </row>
@@ -5173,13 +5167,13 @@
         <v>7</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>90</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>91</v>
       </c>
       <c r="E23" s="11"/>
     </row>
@@ -5188,13 +5182,13 @@
         <v>7</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="13" t="s">
         <v>92</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>93</v>
       </c>
       <c r="E24" s="11"/>
     </row>
@@ -5203,13 +5197,13 @@
         <v>7</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="13" t="s">
         <v>94</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>95</v>
       </c>
       <c r="E25" s="11"/>
     </row>
@@ -5218,13 +5212,13 @@
         <v>7</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="13" t="s">
         <v>96</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>97</v>
       </c>
       <c r="E26" s="11"/>
     </row>
@@ -5233,13 +5227,13 @@
         <v>7</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="13" t="s">
         <v>98</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>99</v>
       </c>
       <c r="E27" s="11"/>
     </row>
@@ -5248,13 +5242,13 @@
         <v>7</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="13" t="s">
         <v>100</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>101</v>
       </c>
       <c r="E28" s="11"/>
     </row>
@@ -5263,13 +5257,13 @@
         <v>7</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="13" t="s">
         <v>102</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>103</v>
       </c>
       <c r="E29" s="11"/>
     </row>
@@ -5278,13 +5272,13 @@
         <v>7</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>104</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>105</v>
       </c>
       <c r="E30" s="11"/>
     </row>
@@ -5293,13 +5287,13 @@
         <v>7</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>107</v>
       </c>
       <c r="E31" s="11"/>
     </row>
@@ -5308,13 +5302,13 @@
         <v>7</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="13" t="s">
         <v>108</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>109</v>
       </c>
       <c r="E32" s="11"/>
     </row>
@@ -5323,13 +5317,13 @@
         <v>7</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" s="13" t="s">
         <v>110</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>111</v>
       </c>
       <c r="E33" s="11"/>
     </row>
@@ -5338,13 +5332,13 @@
         <v>7</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="13" t="s">
         <v>112</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>113</v>
       </c>
       <c r="E34" s="11"/>
     </row>
@@ -5353,13 +5347,13 @@
         <v>7</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="13" t="s">
         <v>114</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>115</v>
       </c>
       <c r="E35" s="11"/>
     </row>
@@ -5368,13 +5362,13 @@
         <v>7</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="13" t="s">
         <v>116</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>117</v>
       </c>
       <c r="E36" s="11"/>
     </row>
@@ -5383,13 +5377,13 @@
         <v>7</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="13" t="s">
         <v>118</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>119</v>
       </c>
       <c r="E37" s="11"/>
     </row>
@@ -5398,13 +5392,13 @@
         <v>7</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" s="13" t="s">
         <v>120</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>121</v>
       </c>
       <c r="E38" s="11"/>
     </row>
@@ -5413,13 +5407,13 @@
         <v>7</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" s="13" t="s">
         <v>122</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>123</v>
       </c>
       <c r="E39" s="11"/>
     </row>
@@ -5428,13 +5422,13 @@
         <v>7</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40" s="13" t="s">
         <v>124</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>125</v>
       </c>
       <c r="E40" s="11"/>
     </row>
@@ -5443,13 +5437,13 @@
         <v>7</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41" s="13" t="s">
         <v>126</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>127</v>
       </c>
       <c r="E41" s="11"/>
     </row>
@@ -5458,13 +5452,13 @@
         <v>7</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D42" s="13" t="s">
         <v>128</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>129</v>
       </c>
       <c r="E42" s="11"/>
     </row>
@@ -5473,13 +5467,13 @@
         <v>7</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43" s="13" t="s">
         <v>130</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>131</v>
       </c>
       <c r="E43" s="11"/>
     </row>
@@ -5488,13 +5482,13 @@
         <v>7</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44" s="13" t="s">
         <v>132</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="E44" s="11"/>
     </row>
@@ -5503,13 +5497,13 @@
         <v>7</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D45" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>135</v>
       </c>
       <c r="E45" s="11"/>
     </row>
@@ -5518,13 +5512,13 @@
         <v>7</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" s="13" t="s">
         <v>136</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>137</v>
       </c>
       <c r="E46" s="11"/>
     </row>
@@ -5533,13 +5527,13 @@
         <v>7</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D47" s="13" t="s">
         <v>138</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>139</v>
       </c>
       <c r="E47" s="11"/>
     </row>
@@ -5548,13 +5542,13 @@
         <v>7</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D48" s="13" t="s">
         <v>140</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>141</v>
       </c>
       <c r="E48" s="11"/>
     </row>
@@ -5563,13 +5557,13 @@
         <v>7</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D49" s="13" t="s">
         <v>142</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>143</v>
       </c>
       <c r="E49" s="11"/>
     </row>
@@ -5578,13 +5572,13 @@
         <v>7</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D50" s="13" t="s">
         <v>144</v>
-      </c>
-      <c r="C50" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>145</v>
       </c>
       <c r="E50" s="11"/>
     </row>
@@ -5618,7 +5612,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="35.450000000000003" customHeight="1">
       <c r="A1" s="148" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B1" s="149"/>
       <c r="C1" s="149"/>
@@ -5628,20 +5622,20 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="150" t="s">
         <v>43</v>
-      </c>
-      <c r="C2" s="150" t="s">
-        <v>44</v>
       </c>
       <c r="D2" s="151"/>
       <c r="E2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="67.150000000000006" customHeight="1">
@@ -5649,17 +5643,17 @@
         <v>1</v>
       </c>
       <c r="B3" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" s="152" t="s">
         <v>147</v>
-      </c>
-      <c r="C3" s="152" t="s">
-        <v>148</v>
       </c>
       <c r="D3" s="153"/>
       <c r="E3" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="72.75" customHeight="1">
@@ -5667,17 +5661,17 @@
         <v>2</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C4" s="152" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D4" s="153"/>
       <c r="E4" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" s="19" t="s">
         <v>151</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5690,7 +5684,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="147" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B6" s="147"/>
       <c r="C6" s="147"/>
@@ -5703,19 +5697,19 @@
         <v>31</v>
       </c>
       <c r="B7" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="D7" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="E7" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="109" t="s">
         <v>154</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="109" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="29.25">
@@ -5723,16 +5717,16 @@
         <v>8</v>
       </c>
       <c r="B8" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="103" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="103" t="s">
+      <c r="D8" s="111" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="24" t="s">
         <v>157</v>
-      </c>
-      <c r="D8" s="111" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>158</v>
       </c>
       <c r="F8" s="110"/>
     </row>
@@ -5741,16 +5735,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="C9" s="103" t="s">
+        <v>156</v>
+      </c>
+      <c r="D9" s="111" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="24" t="s">
         <v>159</v>
-      </c>
-      <c r="C9" s="103" t="s">
-        <v>157</v>
-      </c>
-      <c r="D9" s="111" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>160</v>
       </c>
       <c r="F9" s="110"/>
     </row>
@@ -5759,16 +5753,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" s="103" t="s">
         <v>161</v>
       </c>
-      <c r="C10" s="103" t="s">
+      <c r="D10" s="111" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="24" t="s">
         <v>162</v>
-      </c>
-      <c r="D10" s="111" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>163</v>
       </c>
       <c r="F10" s="110"/>
     </row>
@@ -5777,16 +5771,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="103" t="s">
+        <v>161</v>
+      </c>
+      <c r="D11" s="112" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="24" t="s">
         <v>164</v>
-      </c>
-      <c r="C11" s="103" t="s">
-        <v>162</v>
-      </c>
-      <c r="D11" s="112" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>165</v>
       </c>
       <c r="F11" s="110"/>
     </row>
@@ -5822,7 +5816,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="36" customHeight="1">
       <c r="A1" s="156" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B1" s="157"/>
       <c r="C1" s="157"/>
@@ -5832,20 +5826,20 @@
     </row>
     <row r="2" spans="1:6" ht="22.15" customHeight="1">
       <c r="A2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="150" t="s">
         <v>43</v>
-      </c>
-      <c r="C2" s="150" t="s">
-        <v>44</v>
       </c>
       <c r="D2" s="151"/>
       <c r="E2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="223.15" customHeight="1">
@@ -5853,14 +5847,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="106" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="158" t="s">
         <v>167</v>
-      </c>
-      <c r="C3" s="158" t="s">
-        <v>168</v>
       </c>
       <c r="D3" s="159"/>
       <c r="E3" s="106" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F3" s="106"/>
     </row>
@@ -5869,22 +5863,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="107" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="160" t="s">
         <v>169</v>
-      </c>
-      <c r="C4" s="160" t="s">
-        <v>170</v>
       </c>
       <c r="D4" s="161"/>
       <c r="E4" s="107" t="s">
+        <v>170</v>
+      </c>
+      <c r="F4" s="107" t="s">
         <v>171</v>
-      </c>
-      <c r="F4" s="107" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="150" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B6" s="162"/>
       <c r="C6" s="162"/>
@@ -5897,135 +5891,135 @@
         <v>31</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="25.9" customHeight="1">
       <c r="A8" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C8" s="103" t="s">
+        <v>161</v>
+      </c>
+      <c r="D8" s="105" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="19" t="s">
         <v>174</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="C8" s="103" t="s">
-        <v>162</v>
-      </c>
-      <c r="D8" s="105" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="77.45" customHeight="1">
       <c r="A9" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B9" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" s="103" t="s">
+        <v>156</v>
+      </c>
+      <c r="D9" s="104" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="19" t="s">
         <v>176</v>
-      </c>
-      <c r="C9" s="103" t="s">
-        <v>157</v>
-      </c>
-      <c r="D9" s="104" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="95.45" customHeight="1">
       <c r="A10" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B10" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="C10" s="103" t="s">
         <v>178</v>
       </c>
-      <c r="C10" s="103" t="s">
+      <c r="D10" s="104" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="19" t="s">
         <v>179</v>
-      </c>
-      <c r="D10" s="104" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="125.45" customHeight="1">
       <c r="A11" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B11" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="C11" s="103" t="s">
         <v>181</v>
       </c>
-      <c r="C11" s="103" t="s">
+      <c r="D11" s="104" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="19" t="s">
         <v>182</v>
-      </c>
-      <c r="D11" s="104" t="s">
-        <v>80</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="80.45" customHeight="1">
       <c r="A12" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B12" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C12" s="103" t="s">
+        <v>156</v>
+      </c>
+      <c r="D12" s="104" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="19" t="s">
         <v>184</v>
-      </c>
-      <c r="C12" s="103" t="s">
-        <v>157</v>
-      </c>
-      <c r="D12" s="104" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="25.9" customHeight="1">
       <c r="A13" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B13" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="C13" s="103" t="s">
         <v>186</v>
       </c>
-      <c r="C13" s="103" t="s">
+      <c r="D13" s="104" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="19" t="s">
         <v>187</v>
-      </c>
-      <c r="D13" s="104" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="25.15" customHeight="1">
       <c r="A14" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B14" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="C14" s="103" t="s">
+        <v>156</v>
+      </c>
+      <c r="D14" s="104" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="19" t="s">
         <v>189</v>
-      </c>
-      <c r="C14" s="103" t="s">
-        <v>157</v>
-      </c>
-      <c r="D14" s="104" t="s">
-        <v>80</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -6059,7 +6053,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="43.15" customHeight="1">
       <c r="A1" s="148" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B1" s="148"/>
       <c r="C1" s="148"/>
@@ -6069,20 +6063,20 @@
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1">
       <c r="A2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="150" t="s">
         <v>43</v>
-      </c>
-      <c r="C2" s="150" t="s">
-        <v>44</v>
       </c>
       <c r="D2" s="151"/>
       <c r="E2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="56.25" customHeight="1">
@@ -6092,15 +6086,15 @@
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="166" t="s">
+      <c r="C3" s="163" t="s">
+        <v>191</v>
+      </c>
+      <c r="D3" s="164"/>
+      <c r="E3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="D3" s="167"/>
-      <c r="E3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="53.25" customHeight="1">
@@ -6110,15 +6104,15 @@
       <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="166" t="s">
+      <c r="C4" s="163" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="164"/>
+      <c r="E4" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="D4" s="167"/>
-      <c r="E4" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="33" customHeight="1">
@@ -6128,15 +6122,15 @@
       <c r="B5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="166" t="s">
-        <v>168</v>
-      </c>
-      <c r="D5" s="167"/>
+      <c r="C5" s="163" t="s">
+        <v>167</v>
+      </c>
+      <c r="D5" s="164"/>
       <c r="E5" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="135.75" customHeight="1">
@@ -6144,17 +6138,17 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" s="163" t="s">
         <v>197</v>
       </c>
-      <c r="C6" s="166" t="s">
+      <c r="D6" s="164"/>
+      <c r="E6" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="D6" s="167"/>
-      <c r="E6" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="138.75" customHeight="1">
@@ -6162,17 +6156,17 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C7" s="163" t="s">
         <v>200</v>
       </c>
-      <c r="C7" s="166" t="s">
+      <c r="D7" s="164"/>
+      <c r="E7" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="D7" s="167"/>
-      <c r="E7" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="129.75" customHeight="1">
@@ -6180,17 +6174,17 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C8" s="163" t="s">
         <v>203</v>
       </c>
-      <c r="C8" s="166" t="s">
+      <c r="D8" s="164"/>
+      <c r="E8" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="D8" s="167"/>
-      <c r="E8" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="151.5" customHeight="1">
@@ -6198,28 +6192,28 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C9" s="163" t="s">
         <v>206</v>
       </c>
-      <c r="C9" s="166" t="s">
+      <c r="D9" s="164"/>
+      <c r="E9" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F9" s="21" t="s">
         <v>207</v>
-      </c>
-      <c r="D9" s="167"/>
-      <c r="E9" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="39.6" customHeight="1"/>
     <row r="11" spans="1:6" ht="29.25" customHeight="1">
-      <c r="A11" s="163" t="s">
-        <v>209</v>
-      </c>
-      <c r="B11" s="164"/>
-      <c r="C11" s="164"/>
-      <c r="D11" s="164"/>
-      <c r="E11" s="165"/>
+      <c r="A11" s="165" t="s">
+        <v>208</v>
+      </c>
+      <c r="B11" s="166"/>
+      <c r="C11" s="166"/>
+      <c r="D11" s="166"/>
+      <c r="E11" s="167"/>
       <c r="F11" s="1"/>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1">
@@ -6227,788 +6221,788 @@
         <v>31</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="D12" s="6" t="s">
+      <c r="E12" s="23" t="s">
         <v>55</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>56</v>
       </c>
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:6" ht="40.15" customHeight="1">
       <c r="A13" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="22" t="s">
+      <c r="D13" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="24" t="s">
         <v>211</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>212</v>
       </c>
       <c r="F13" s="1"/>
     </row>
     <row r="14" spans="1:6" ht="40.15" customHeight="1">
       <c r="A14" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D14" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F14" s="1"/>
     </row>
     <row r="15" spans="1:6" ht="40.15" customHeight="1">
       <c r="A15" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D15" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F15" s="1"/>
     </row>
     <row r="16" spans="1:6" ht="40.15" customHeight="1">
       <c r="A16" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D16" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F16" s="1"/>
     </row>
     <row r="17" spans="1:6" ht="40.15" customHeight="1">
       <c r="A17" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B17" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D17" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F17" s="1"/>
     </row>
     <row r="18" spans="1:6" ht="40.15" customHeight="1">
       <c r="A18" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B18" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D18" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F18" s="1"/>
     </row>
     <row r="19" spans="1:6" ht="40.15" customHeight="1">
       <c r="A19" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C19" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" s="24" t="s">
         <v>218</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>219</v>
       </c>
       <c r="F19" s="1"/>
     </row>
     <row r="20" spans="1:6" ht="40.15" customHeight="1">
       <c r="A20" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B20" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D20" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F20" s="1"/>
     </row>
     <row r="21" spans="1:6" ht="27.75" customHeight="1">
       <c r="A21" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B21" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D21" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F21" s="1"/>
     </row>
     <row r="22" spans="1:6" ht="52.5" customHeight="1">
       <c r="A22" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B22" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D22" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="E22" s="24" t="s">
         <v>222</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>223</v>
       </c>
       <c r="F22" s="1"/>
     </row>
     <row r="23" spans="1:6" ht="40.15" customHeight="1">
       <c r="A23" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B23" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D23" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F23" s="1"/>
     </row>
     <row r="24" spans="1:6" ht="40.15" customHeight="1">
       <c r="A24" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C24" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" s="24" t="s">
         <v>225</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>226</v>
       </c>
       <c r="F24" s="1"/>
     </row>
     <row r="25" spans="1:6" ht="40.15" customHeight="1">
       <c r="A25" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F25" s="1"/>
     </row>
     <row r="26" spans="1:6" ht="40.15" customHeight="1">
       <c r="A26" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F26" s="1"/>
     </row>
     <row r="27" spans="1:6" ht="40.15" customHeight="1">
       <c r="A27" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C27" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" s="24" t="s">
         <v>229</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E27" s="24" t="s">
-        <v>230</v>
       </c>
       <c r="F27" s="1"/>
     </row>
     <row r="28" spans="1:6" ht="40.15" customHeight="1">
       <c r="A28" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F28" s="1"/>
     </row>
     <row r="29" spans="1:6" ht="40.15" customHeight="1">
       <c r="A29" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C29" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29" s="24" t="s">
         <v>232</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="24" t="s">
-        <v>233</v>
       </c>
       <c r="F29" s="1"/>
     </row>
     <row r="30" spans="1:6" ht="40.15" customHeight="1">
       <c r="A30" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F30" s="1"/>
     </row>
     <row r="31" spans="1:6" ht="40.15" customHeight="1">
       <c r="A31" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C31" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E31" s="24" t="s">
         <v>235</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E31" s="24" t="s">
-        <v>236</v>
       </c>
       <c r="F31" s="1"/>
     </row>
     <row r="32" spans="1:6" ht="40.15" customHeight="1">
       <c r="A32" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B32" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D32" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F32" s="1"/>
     </row>
     <row r="33" spans="1:6" ht="40.15" customHeight="1">
       <c r="A33" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C33" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B33" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D33" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F33" s="1"/>
     </row>
     <row r="34" spans="1:6" ht="40.15" customHeight="1">
       <c r="A34" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B34" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="C34" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D34" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F34" s="1"/>
     </row>
     <row r="35" spans="1:6" ht="39" customHeight="1">
       <c r="A35" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F35" s="1"/>
     </row>
     <row r="36" spans="1:6" ht="40.15" customHeight="1">
       <c r="A36" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D36" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F36" s="1"/>
     </row>
     <row r="37" spans="1:6" ht="40.15" customHeight="1">
       <c r="A37" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D37" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E37" s="24" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F37" s="1"/>
     </row>
     <row r="38" spans="1:6" ht="34.5" customHeight="1">
       <c r="A38" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C38" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" s="24" t="s">
         <v>243</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E38" s="24" t="s">
-        <v>244</v>
       </c>
       <c r="F38" s="1"/>
     </row>
     <row r="39" spans="1:6" ht="40.15" customHeight="1">
       <c r="A39" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E39" s="24" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F39" s="1"/>
     </row>
     <row r="40" spans="1:6" ht="40.15" customHeight="1">
       <c r="A40" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D40" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F40" s="1"/>
     </row>
     <row r="41" spans="1:6" ht="40.15" customHeight="1">
       <c r="A41" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E41" s="24" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F41" s="1"/>
     </row>
     <row r="42" spans="1:6" ht="40.15" customHeight="1">
       <c r="A42" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C42" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B42" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="C42" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D42" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E42" s="24" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F42" s="1"/>
     </row>
     <row r="43" spans="1:6" ht="40.15" customHeight="1">
       <c r="A43" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B43" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="C43" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D43" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E43" s="24" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F43" s="1"/>
     </row>
     <row r="44" spans="1:6" ht="40.15" customHeight="1">
       <c r="A44" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C44" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="D44" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="24" t="s">
         <v>250</v>
-      </c>
-      <c r="D44" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E44" s="24" t="s">
-        <v>251</v>
       </c>
       <c r="F44" s="1"/>
     </row>
     <row r="45" spans="1:6" ht="40.15" customHeight="1">
       <c r="A45" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C45" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="D45" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45" s="24" t="s">
         <v>252</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E45" s="24" t="s">
-        <v>253</v>
       </c>
       <c r="F45" s="1"/>
     </row>
     <row r="46" spans="1:6" ht="25.5" customHeight="1">
       <c r="A46" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C46" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E46" s="24" t="s">
         <v>254</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E46" s="24" t="s">
-        <v>255</v>
       </c>
       <c r="F46" s="1"/>
     </row>
     <row r="47" spans="1:6" ht="28.15" customHeight="1">
       <c r="A47" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C47" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B47" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="C47" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D47" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E47" s="24" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F47" s="1"/>
     </row>
     <row r="48" spans="1:6" ht="27.6" customHeight="1">
       <c r="A48" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="C48" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B48" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="C48" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D48" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E48" s="24" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F48" s="1"/>
     </row>
     <row r="49" spans="1:6" ht="36" customHeight="1">
       <c r="A49" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="C49" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B49" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="C49" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D49" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E49" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F49" s="1"/>
     </row>
     <row r="50" spans="1:6" ht="25.9" customHeight="1">
       <c r="A50" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C50" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B50" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D50" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F50" s="1"/>
     </row>
     <row r="51" spans="1:6" ht="25.9" customHeight="1">
       <c r="A51" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B51" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C51" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B51" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D51" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E51" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F51" s="1"/>
     </row>
     <row r="52" spans="1:6" ht="60.75" customHeight="1">
       <c r="A52" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E52" s="24" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F52" s="1"/>
     </row>
     <row r="53" spans="1:6" ht="29.45" customHeight="1">
       <c r="A53" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B53" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="C53" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="D53" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E53" s="24" t="s">
         <v>262</v>
-      </c>
-      <c r="C53" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="D53" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="E53" s="24" t="s">
-        <v>263</v>
       </c>
       <c r="F53" s="1"/>
     </row>
     <row r="54" spans="1:6" ht="30.6" customHeight="1">
       <c r="A54" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C54" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B54" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="C54" s="22" t="s">
-        <v>211</v>
-      </c>
       <c r="D54" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" s="24" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F54" s="1"/>
     </row>
     <row r="55" spans="1:6"/>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7033,7 +7027,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="37.5" customHeight="1">
       <c r="A1" s="168" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B1" s="169"/>
       <c r="C1" s="169"/>
@@ -7043,20 +7037,20 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="C2" s="170" t="s">
         <v>43</v>
-      </c>
-      <c r="C2" s="170" t="s">
-        <v>44</v>
       </c>
       <c r="D2" s="171"/>
       <c r="E2" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="33" t="s">
         <v>45</v>
-      </c>
-      <c r="F2" s="33" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="21" customHeight="1">
@@ -7069,10 +7063,10 @@
       <c r="C3" s="172"/>
       <c r="D3" s="173"/>
       <c r="E3" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -7085,7 +7079,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="169" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B5" s="169"/>
       <c r="C5" s="169"/>
@@ -7098,16 +7092,16 @@
         <v>31</v>
       </c>
       <c r="B6" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="33" t="s">
-        <v>154</v>
-      </c>
-      <c r="D6" s="33" t="s">
+      <c r="E6" s="34" t="s">
         <v>55</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>56</v>
       </c>
       <c r="F6" s="26"/>
     </row>
@@ -7116,16 +7110,16 @@
         <v>12</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F7" s="27"/>
     </row>
@@ -7134,16 +7128,16 @@
         <v>12</v>
       </c>
       <c r="B8" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="C8" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="C8" s="16" t="s">
-        <v>270</v>
-      </c>
       <c r="D8" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F8" s="27"/>
     </row>
@@ -7152,16 +7146,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="16" t="s">
-        <v>272</v>
-      </c>
       <c r="D9" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F9" s="27"/>
     </row>
@@ -7170,16 +7164,16 @@
         <v>12</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F10" s="27"/>
     </row>
@@ -7188,16 +7182,16 @@
         <v>12</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F11" s="27"/>
     </row>
@@ -7206,16 +7200,16 @@
         <v>12</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F12" s="27"/>
     </row>
@@ -7224,16 +7218,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F13" s="27"/>
     </row>
@@ -7242,16 +7236,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F14" s="27"/>
     </row>
@@ -7260,16 +7254,16 @@
         <v>12</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F15" s="27"/>
     </row>
@@ -7278,16 +7272,16 @@
         <v>12</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F16" s="27"/>
     </row>
@@ -7296,16 +7290,16 @@
         <v>12</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F17" s="27"/>
     </row>
@@ -7314,16 +7308,16 @@
         <v>12</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F18" s="27"/>
     </row>
@@ -7332,16 +7326,16 @@
         <v>12</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F19" s="27"/>
     </row>
@@ -7350,16 +7344,16 @@
         <v>12</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F20" s="27"/>
     </row>
@@ -7368,16 +7362,16 @@
         <v>12</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F21" s="27"/>
     </row>
@@ -7386,16 +7380,16 @@
         <v>12</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F22" s="27"/>
     </row>
@@ -7404,16 +7398,16 @@
         <v>12</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F23" s="27"/>
     </row>
@@ -7422,16 +7416,16 @@
         <v>12</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F24" s="27"/>
     </row>
@@ -7440,16 +7434,16 @@
         <v>12</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F25" s="27"/>
     </row>
@@ -7458,16 +7452,16 @@
         <v>12</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F26" s="27"/>
     </row>
@@ -7476,16 +7470,16 @@
         <v>12</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F27" s="27"/>
     </row>
@@ -7494,16 +7488,16 @@
         <v>12</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F28" s="27"/>
     </row>
@@ -7512,16 +7506,16 @@
         <v>12</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F29" s="27"/>
     </row>
@@ -7530,16 +7524,16 @@
         <v>12</v>
       </c>
       <c r="B30" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="C30" s="16" t="s">
         <v>290</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>291</v>
-      </c>
       <c r="D30" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F30" s="27"/>
     </row>
@@ -7548,16 +7542,16 @@
         <v>12</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C31" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="E31" s="28" t="s">
         <v>291</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="E31" s="28" t="s">
-        <v>292</v>
       </c>
       <c r="F31" s="27"/>
     </row>
@@ -7566,16 +7560,16 @@
         <v>12</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F32" s="27"/>
     </row>
@@ -7584,16 +7578,16 @@
         <v>12</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F33" s="27"/>
     </row>
@@ -7602,16 +7596,16 @@
         <v>12</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F34" s="27"/>
     </row>
@@ -7620,16 +7614,16 @@
         <v>12</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35" s="28" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F35" s="27"/>
     </row>
@@ -7638,16 +7632,16 @@
         <v>12</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E36" s="28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F36" s="27"/>
     </row>
@@ -7656,16 +7650,16 @@
         <v>12</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E37" s="28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F37" s="27"/>
     </row>
@@ -7674,16 +7668,16 @@
         <v>12</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E38" s="28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F38" s="27"/>
     </row>
@@ -7692,16 +7686,16 @@
         <v>12</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F39" s="27"/>
     </row>
@@ -7710,16 +7704,16 @@
         <v>12</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F40" s="27"/>
     </row>
@@ -7728,16 +7722,16 @@
         <v>12</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E41" s="28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F41" s="27"/>
     </row>
@@ -7746,16 +7740,16 @@
         <v>12</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E42" s="28" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F42" s="27"/>
     </row>
@@ -7764,16 +7758,16 @@
         <v>12</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E43" s="28" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F43" s="27"/>
     </row>
@@ -7782,16 +7776,16 @@
         <v>12</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E44" s="28" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F44" s="27"/>
     </row>
@@ -7800,16 +7794,16 @@
         <v>12</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E45" s="28" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F45" s="27"/>
     </row>
@@ -7818,16 +7812,16 @@
         <v>12</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D46" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E46" s="28" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F46" s="27"/>
     </row>
@@ -7836,16 +7830,16 @@
         <v>12</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F47" s="27"/>
     </row>
@@ -7854,16 +7848,16 @@
         <v>12</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E48" s="28" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F48" s="27"/>
     </row>
@@ -7872,16 +7866,16 @@
         <v>12</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E49" s="28" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F49" s="27"/>
     </row>
@@ -7890,16 +7884,16 @@
         <v>12</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E50" s="28" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F50" s="27"/>
     </row>
@@ -7908,16 +7902,16 @@
         <v>12</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E51" s="28" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F51" s="27"/>
     </row>
@@ -7926,16 +7920,16 @@
         <v>12</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E52" s="28" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F52" s="27"/>
     </row>
@@ -7944,16 +7938,16 @@
         <v>12</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E53" s="28" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F53" s="27"/>
     </row>
@@ -7962,16 +7956,16 @@
         <v>12</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" s="28" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F54" s="27"/>
     </row>
@@ -7980,16 +7974,16 @@
         <v>12</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E55" s="28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F55" s="27"/>
     </row>
@@ -7998,16 +7992,16 @@
         <v>12</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E56" s="28" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F56" s="27"/>
     </row>
@@ -8016,16 +8010,16 @@
         <v>12</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E57" s="28" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F57" s="27"/>
     </row>
@@ -8034,16 +8028,16 @@
         <v>12</v>
       </c>
       <c r="B58" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="C58" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="C58" s="16" t="s">
-        <v>316</v>
-      </c>
       <c r="D58" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F58" s="27"/>
     </row>
@@ -8052,16 +8046,16 @@
         <v>12</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E59" s="28" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F59" s="27"/>
     </row>
@@ -8070,16 +8064,16 @@
         <v>12</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E60" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F60" s="27"/>
     </row>
@@ -8088,16 +8082,16 @@
         <v>12</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E61" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F61" s="27"/>
     </row>
@@ -8106,16 +8100,16 @@
         <v>12</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E62" s="28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F62" s="27"/>
     </row>
@@ -8124,16 +8118,16 @@
         <v>12</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E63" s="28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F63" s="27"/>
     </row>
@@ -8142,16 +8136,16 @@
         <v>12</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E64" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F64" s="27"/>
     </row>
@@ -8160,16 +8154,16 @@
         <v>12</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E65" s="28" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F65" s="27"/>
     </row>
@@ -8178,16 +8172,16 @@
         <v>12</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E66" s="28" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F66" s="27"/>
     </row>
@@ -8196,16 +8190,16 @@
         <v>12</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D67" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E67" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F67" s="27"/>
     </row>
@@ -8214,16 +8208,16 @@
         <v>12</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D68" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E68" s="28" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F68" s="27"/>
     </row>
@@ -8232,16 +8226,16 @@
         <v>12</v>
       </c>
       <c r="B69" s="16" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D69" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E69" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F69" s="27"/>
     </row>
@@ -8250,16 +8244,16 @@
         <v>12</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D70" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E70" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F70" s="27"/>
     </row>
@@ -8268,16 +8262,16 @@
         <v>12</v>
       </c>
       <c r="B71" s="16" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D71" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E71" s="28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F71" s="27"/>
     </row>
@@ -8286,16 +8280,16 @@
         <v>12</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C72" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D72" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E72" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F72" s="27"/>
     </row>
@@ -8304,16 +8298,16 @@
         <v>12</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C73" s="16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D73" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E73" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F73" s="27"/>
     </row>
@@ -8346,7 +8340,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" customHeight="1">
       <c r="A1" s="174" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B1" s="175"/>
       <c r="C1" s="175"/>
@@ -8356,20 +8350,20 @@
     </row>
     <row r="2" spans="1:6" ht="18.75">
       <c r="A2" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="C2" s="175" t="s">
         <v>43</v>
-      </c>
-      <c r="C2" s="175" t="s">
-        <v>44</v>
       </c>
       <c r="D2" s="175"/>
       <c r="E2" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="35" t="s">
         <v>45</v>
-      </c>
-      <c r="F2" s="35" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="21" customHeight="1">
@@ -8382,7 +8376,7 @@
     </row>
     <row r="4" spans="1:6" ht="18.75">
       <c r="A4" s="175" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B4" s="175"/>
       <c r="C4" s="175"/>
@@ -8395,16 +8389,16 @@
         <v>31</v>
       </c>
       <c r="B5" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="D5" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="D5" s="35" t="s">
+      <c r="E5" s="35" t="s">
         <v>55</v>
-      </c>
-      <c r="E5" s="35" t="s">
-        <v>56</v>
       </c>
       <c r="F5" s="114"/>
     </row>
@@ -8413,16 +8407,16 @@
         <v>13</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E6" s="41" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F6" s="115"/>
     </row>
@@ -8431,16 +8425,16 @@
         <v>13</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F7" s="115"/>
     </row>
@@ -8449,16 +8443,16 @@
         <v>13</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D8" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" s="41" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F8" s="115"/>
     </row>
@@ -8467,16 +8461,16 @@
         <v>13</v>
       </c>
       <c r="B9" s="41" t="s">
+        <v>268</v>
+      </c>
+      <c r="C9" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="C9" s="41" t="s">
-        <v>270</v>
-      </c>
       <c r="D9" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" s="41" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F9" s="115"/>
     </row>
@@ -8485,16 +8479,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" s="41" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F10" s="115"/>
     </row>
@@ -8503,16 +8497,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D11" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E11" s="41" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F11" s="115"/>
     </row>
@@ -8521,16 +8515,16 @@
         <v>13</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C12" s="41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D12" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F12" s="115"/>
     </row>
@@ -8539,16 +8533,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D13" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F13" s="115"/>
     </row>
@@ -8557,16 +8551,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D14" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F14" s="115"/>
     </row>
@@ -8575,16 +8569,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D15" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F15" s="115"/>
     </row>
@@ -8593,16 +8587,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F16" s="115"/>
     </row>
@@ -8611,16 +8605,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D17" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F17" s="115"/>
     </row>
@@ -8629,16 +8623,16 @@
         <v>13</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D18" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F18" s="115"/>
     </row>
@@ -8647,16 +8641,16 @@
         <v>13</v>
       </c>
       <c r="B19" s="41" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D19" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F19" s="115"/>
     </row>
@@ -8665,16 +8659,16 @@
         <v>13</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D20" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F20" s="115"/>
     </row>
@@ -8683,16 +8677,16 @@
         <v>13</v>
       </c>
       <c r="B21" s="41" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D21" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F21" s="115"/>
     </row>
@@ -8701,16 +8695,16 @@
         <v>13</v>
       </c>
       <c r="B22" s="41" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D22" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F22" s="115"/>
     </row>
@@ -8719,16 +8713,16 @@
         <v>13</v>
       </c>
       <c r="B23" s="41" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D23" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F23" s="115"/>
     </row>
@@ -8737,16 +8731,16 @@
         <v>13</v>
       </c>
       <c r="B24" s="41" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D24" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" s="41" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F24" s="115"/>
     </row>
@@ -8755,16 +8749,16 @@
         <v>13</v>
       </c>
       <c r="B25" s="41" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D25" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F25" s="115"/>
     </row>
@@ -8773,16 +8767,16 @@
         <v>13</v>
       </c>
       <c r="B26" s="41" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C26" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D26" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" s="41" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F26" s="115"/>
     </row>
@@ -8791,16 +8785,16 @@
         <v>13</v>
       </c>
       <c r="B27" s="41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D27" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E27" s="41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F27" s="115"/>
     </row>
@@ -8809,16 +8803,16 @@
         <v>13</v>
       </c>
       <c r="B28" s="41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C28" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D28" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F28" s="115"/>
     </row>
@@ -8827,16 +8821,16 @@
         <v>13</v>
       </c>
       <c r="B29" s="41" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D29" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E29" s="41" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F29" s="115"/>
     </row>
@@ -8845,16 +8839,16 @@
         <v>13</v>
       </c>
       <c r="B30" s="41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D30" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E30" s="41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F30" s="115"/>
     </row>
@@ -8863,16 +8857,16 @@
         <v>13</v>
       </c>
       <c r="B31" s="41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C31" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D31" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E31" s="41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F31" s="115"/>
     </row>
@@ -8881,16 +8875,16 @@
         <v>13</v>
       </c>
       <c r="B32" s="41" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C32" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D32" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E32" s="41" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F32" s="115"/>
     </row>
@@ -8899,16 +8893,16 @@
         <v>13</v>
       </c>
       <c r="B33" s="41" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C33" s="41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D33" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E33" s="41" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F33" s="115"/>
     </row>
@@ -8917,16 +8911,16 @@
         <v>13</v>
       </c>
       <c r="B34" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D34" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E34" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F34" s="115"/>
     </row>
@@ -8935,16 +8929,16 @@
         <v>13</v>
       </c>
       <c r="B35" s="41" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C35" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D35" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35" s="41" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F35" s="115"/>
     </row>
@@ -8953,16 +8947,16 @@
         <v>13</v>
       </c>
       <c r="B36" s="41" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C36" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D36" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E36" s="41" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F36" s="115"/>
     </row>
@@ -8971,16 +8965,16 @@
         <v>13</v>
       </c>
       <c r="B37" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C37" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="D37" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="E37" s="41" t="s">
         <v>291</v>
-      </c>
-      <c r="D37" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="E37" s="41" t="s">
-        <v>292</v>
       </c>
       <c r="F37" s="115"/>
     </row>
@@ -8989,16 +8983,16 @@
         <v>13</v>
       </c>
       <c r="B38" s="41" t="s">
+        <v>289</v>
+      </c>
+      <c r="C38" s="41" t="s">
         <v>290</v>
       </c>
-      <c r="C38" s="41" t="s">
-        <v>291</v>
-      </c>
       <c r="D38" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E38" s="41" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F38" s="115"/>
     </row>
@@ -9007,16 +9001,16 @@
         <v>13</v>
       </c>
       <c r="B39" s="41" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D39" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E39" s="41" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F39" s="115"/>
     </row>
@@ -9025,16 +9019,16 @@
         <v>13</v>
       </c>
       <c r="B40" s="41" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C40" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D40" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E40" s="41" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F40" s="115"/>
     </row>
@@ -9043,16 +9037,16 @@
         <v>13</v>
       </c>
       <c r="B41" s="41" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C41" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D41" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E41" s="41" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F41" s="115"/>
     </row>
@@ -9061,16 +9055,16 @@
         <v>13</v>
       </c>
       <c r="B42" s="41" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C42" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D42" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E42" s="41" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F42" s="115"/>
     </row>
@@ -9079,16 +9073,16 @@
         <v>13</v>
       </c>
       <c r="B43" s="41" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C43" s="41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D43" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E43" s="41" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F43" s="115"/>
     </row>
@@ -9097,16 +9091,16 @@
         <v>13</v>
       </c>
       <c r="B44" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C44" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D44" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E44" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F44" s="115"/>
     </row>
@@ -9115,16 +9109,16 @@
         <v>13</v>
       </c>
       <c r="B45" s="41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C45" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D45" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E45" s="41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F45" s="115"/>
     </row>
@@ -9133,16 +9127,16 @@
         <v>13</v>
       </c>
       <c r="B46" s="41" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D46" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E46" s="41" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F46" s="115"/>
     </row>
@@ -9151,16 +9145,16 @@
         <v>13</v>
       </c>
       <c r="B47" s="41" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C47" s="41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D47" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E47" s="41" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F47" s="115"/>
     </row>
@@ -9169,16 +9163,16 @@
         <v>13</v>
       </c>
       <c r="B48" s="41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C48" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D48" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E48" s="41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F48" s="115"/>
     </row>
@@ -9187,16 +9181,16 @@
         <v>13</v>
       </c>
       <c r="B49" s="41" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C49" s="41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D49" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E49" s="41" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F49" s="115"/>
     </row>
@@ -9205,16 +9199,16 @@
         <v>13</v>
       </c>
       <c r="B50" s="41" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C50" s="41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D50" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E50" s="41" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F50" s="115"/>
     </row>
@@ -9223,16 +9217,16 @@
         <v>13</v>
       </c>
       <c r="B51" s="41" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C51" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D51" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E51" s="41" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F51" s="115"/>
     </row>
@@ -9241,16 +9235,16 @@
         <v>13</v>
       </c>
       <c r="B52" s="41" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C52" s="41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D52" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E52" s="41" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F52" s="115"/>
     </row>
@@ -9259,16 +9253,16 @@
         <v>13</v>
       </c>
       <c r="B53" s="41" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C53" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D53" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E53" s="41" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F53" s="115"/>
     </row>
@@ -9277,16 +9271,16 @@
         <v>13</v>
       </c>
       <c r="B54" s="41" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C54" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D54" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" s="41" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F54" s="115"/>
     </row>
@@ -9295,16 +9289,16 @@
         <v>13</v>
       </c>
       <c r="B55" s="41" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C55" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D55" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E55" s="41" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F55" s="115"/>
     </row>
@@ -9313,16 +9307,16 @@
         <v>13</v>
       </c>
       <c r="B56" s="41" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C56" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D56" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E56" s="41" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F56" s="115"/>
     </row>
@@ -9331,16 +9325,16 @@
         <v>13</v>
       </c>
       <c r="B57" s="41" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C57" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D57" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E57" s="41" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F57" s="115"/>
     </row>
@@ -9349,16 +9343,16 @@
         <v>13</v>
       </c>
       <c r="B58" s="41" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C58" s="41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D58" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E58" s="41" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F58" s="115"/>
     </row>
@@ -9367,16 +9361,16 @@
         <v>13</v>
       </c>
       <c r="B59" s="41" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C59" s="41" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D59" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E59" s="41" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F59" s="115"/>
     </row>
@@ -9385,16 +9379,16 @@
         <v>13</v>
       </c>
       <c r="B60" s="41" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C60" s="41" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D60" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E60" s="41" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F60" s="115"/>
     </row>
@@ -9403,16 +9397,16 @@
         <v>13</v>
       </c>
       <c r="B61" s="41" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C61" s="41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D61" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E61" s="41" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F61" s="115"/>
     </row>
@@ -9421,16 +9415,16 @@
         <v>13</v>
       </c>
       <c r="B62" s="41" t="s">
+        <v>314</v>
+      </c>
+      <c r="C62" s="41" t="s">
         <v>315</v>
       </c>
-      <c r="C62" s="41" t="s">
-        <v>316</v>
-      </c>
       <c r="D62" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E62" s="41" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F62" s="115"/>
     </row>
@@ -9439,16 +9433,16 @@
         <v>13</v>
       </c>
       <c r="B63" s="41" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C63" s="41" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D63" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E63" s="41" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F63" s="115"/>
     </row>
@@ -9457,16 +9451,16 @@
         <v>13</v>
       </c>
       <c r="B64" s="41" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C64" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D64" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E64" s="41" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F64" s="115"/>
     </row>
@@ -9475,16 +9469,16 @@
         <v>13</v>
       </c>
       <c r="B65" s="41" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C65" s="41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D65" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E65" s="41" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F65" s="115"/>
     </row>
@@ -9493,16 +9487,16 @@
         <v>13</v>
       </c>
       <c r="B66" s="41" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C66" s="41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D66" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E66" s="41" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F66" s="115"/>
     </row>
@@ -9511,16 +9505,16 @@
         <v>13</v>
       </c>
       <c r="B67" s="41" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C67" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D67" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E67" s="41" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F67" s="115"/>
     </row>
@@ -9529,16 +9523,16 @@
         <v>13</v>
       </c>
       <c r="B68" s="41" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C68" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D68" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E68" s="41" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F68" s="115"/>
     </row>
@@ -9547,16 +9541,16 @@
         <v>13</v>
       </c>
       <c r="B69" s="41" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C69" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D69" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E69" s="41" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F69" s="115"/>
     </row>
@@ -9565,16 +9559,16 @@
         <v>13</v>
       </c>
       <c r="B70" s="41" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C70" s="41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D70" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E70" s="41" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F70" s="115"/>
     </row>
@@ -9583,16 +9577,16 @@
         <v>13</v>
       </c>
       <c r="B71" s="41" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C71" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D71" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E71" s="41" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F71" s="115"/>
     </row>
@@ -9601,16 +9595,16 @@
         <v>13</v>
       </c>
       <c r="B72" s="41" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C72" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D72" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E72" s="41" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F72" s="115"/>
     </row>
@@ -9644,7 +9638,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="40.5" customHeight="1">
       <c r="A1" s="174" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B1" s="175"/>
       <c r="C1" s="175"/>
@@ -9654,20 +9648,20 @@
     </row>
     <row r="2" spans="1:6" ht="18.75">
       <c r="A2" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="35" t="s">
         <v>42</v>
-      </c>
-      <c r="B2" s="35" t="s">
-        <v>43</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="F2" s="35" t="s">
         <v>45</v>
-      </c>
-      <c r="F2" s="35" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="32.25" customHeight="1">
@@ -9688,7 +9682,7 @@
     </row>
     <row r="5" spans="1:6" ht="18.75">
       <c r="A5" s="175" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B5" s="175"/>
       <c r="C5" s="175"/>
@@ -9701,16 +9695,16 @@
         <v>31</v>
       </c>
       <c r="B6" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="D6" s="35" t="s">
+      <c r="E6" s="35" t="s">
         <v>55</v>
-      </c>
-      <c r="E6" s="35" t="s">
-        <v>56</v>
       </c>
       <c r="F6" s="40"/>
     </row>
@@ -9719,16 +9713,16 @@
         <v>17</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F7" s="36"/>
     </row>
@@ -9737,16 +9731,16 @@
         <v>17</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D8" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" s="41" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F8" s="36"/>
     </row>
@@ -9755,16 +9749,16 @@
         <v>17</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F9" s="36"/>
     </row>
@@ -9773,16 +9767,16 @@
         <v>17</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" s="41" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F10" s="36"/>
     </row>
@@ -9791,16 +9785,16 @@
         <v>17</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D11" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E11" s="41" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F11" s="36"/>
     </row>
@@ -9809,16 +9803,16 @@
         <v>17</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C12" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D12" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F12" s="36"/>
     </row>
@@ -9827,16 +9821,16 @@
         <v>17</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D13" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F13" s="36"/>
     </row>
@@ -9845,16 +9839,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D14" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F14" s="36"/>
     </row>
@@ -9863,16 +9857,16 @@
         <v>17</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D15" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F15" s="36"/>
     </row>
@@ -9881,16 +9875,16 @@
         <v>17</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F16" s="36"/>
     </row>
@@ -9899,16 +9893,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D17" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F17" s="36"/>
     </row>
@@ -9917,16 +9911,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D18" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F18" s="36"/>
     </row>
@@ -9935,16 +9929,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D19" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F19" s="36"/>
     </row>
@@ -9953,16 +9947,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D20" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F20" s="36"/>
     </row>
@@ -9971,16 +9965,16 @@
         <v>17</v>
       </c>
       <c r="B21" s="41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D21" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F21" s="36"/>
     </row>
@@ -9989,16 +9983,16 @@
         <v>17</v>
       </c>
       <c r="B22" s="41" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D22" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F22" s="36"/>
     </row>
@@ -10007,16 +10001,16 @@
         <v>17</v>
       </c>
       <c r="B23" s="41" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D23" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F23" s="36"/>
     </row>
@@ -10025,16 +10019,16 @@
         <v>17</v>
       </c>
       <c r="B24" s="41" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D24" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" s="41" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F24" s="36"/>
     </row>
@@ -10043,16 +10037,16 @@
         <v>17</v>
       </c>
       <c r="B25" s="41" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D25" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F25" s="36"/>
     </row>
@@ -10061,16 +10055,16 @@
         <v>17</v>
       </c>
       <c r="B26" s="41" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C26" s="41" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D26" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" s="41" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F26" s="36"/>
     </row>
@@ -10079,16 +10073,16 @@
         <v>17</v>
       </c>
       <c r="B27" s="41" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D27" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E27" s="41" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F27" s="36"/>
     </row>
@@ -10097,16 +10091,16 @@
         <v>17</v>
       </c>
       <c r="B28" s="41" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C28" s="41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D28" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F28" s="36"/>
     </row>
@@ -10115,16 +10109,16 @@
         <v>17</v>
       </c>
       <c r="B29" s="41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D29" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E29" s="41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F29" s="36"/>
     </row>
@@ -10133,16 +10127,16 @@
         <v>17</v>
       </c>
       <c r="B30" s="41" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D30" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E30" s="41" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F30" s="36"/>
     </row>
@@ -10151,16 +10145,16 @@
         <v>17</v>
       </c>
       <c r="B31" s="41" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C31" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D31" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E31" s="41" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F31" s="36"/>
     </row>
@@ -10169,16 +10163,16 @@
         <v>17</v>
       </c>
       <c r="B32" s="41" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C32" s="41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D32" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E32" s="41" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F32" s="36"/>
     </row>
@@ -10187,16 +10181,16 @@
         <v>17</v>
       </c>
       <c r="B33" s="41" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C33" s="41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D33" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E33" s="41" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F33" s="36"/>
     </row>
@@ -10205,16 +10199,16 @@
         <v>17</v>
       </c>
       <c r="B34" s="41" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D34" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E34" s="41" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F34" s="36"/>
     </row>
@@ -10223,16 +10217,16 @@
         <v>17</v>
       </c>
       <c r="B35" s="41" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C35" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D35" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35" s="41" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F35" s="36"/>
     </row>
@@ -10241,16 +10235,16 @@
         <v>17</v>
       </c>
       <c r="B36" s="41" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C36" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D36" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E36" s="41" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F36" s="36"/>
     </row>
@@ -10259,16 +10253,16 @@
         <v>17</v>
       </c>
       <c r="B37" s="41" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C37" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D37" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E37" s="41" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F37" s="36"/>
     </row>
@@ -10277,16 +10271,16 @@
         <v>17</v>
       </c>
       <c r="B38" s="41" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C38" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D38" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E38" s="41" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F38" s="36"/>
     </row>
@@ -10295,16 +10289,16 @@
         <v>17</v>
       </c>
       <c r="B39" s="41" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D39" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E39" s="41" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F39" s="36"/>
     </row>
@@ -10313,16 +10307,16 @@
         <v>17</v>
       </c>
       <c r="B40" s="41" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C40" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D40" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E40" s="41" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F40" s="36"/>
     </row>
@@ -10331,16 +10325,16 @@
         <v>17</v>
       </c>
       <c r="B41" s="41" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C41" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D41" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E41" s="41" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F41" s="36"/>
     </row>
@@ -10349,16 +10343,16 @@
         <v>17</v>
       </c>
       <c r="B42" s="41" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C42" s="41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D42" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E42" s="41" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F42" s="36"/>
     </row>
@@ -10367,16 +10361,16 @@
         <v>17</v>
       </c>
       <c r="B43" s="41" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C43" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D43" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E43" s="41" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F43" s="36"/>
     </row>
@@ -10385,16 +10379,16 @@
         <v>17</v>
       </c>
       <c r="B44" s="41" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C44" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D44" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E44" s="41" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F44" s="42"/>
     </row>
@@ -10408,6 +10402,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
@@ -10415,15 +10418,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10599,11 +10593,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BD988DF-592B-4F88-8221-BDE140EDD1EA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA282356-BD10-4869-8E2B-473EE5300A0F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA282356-BD10-4869-8E2B-473EE5300A0F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BD988DF-592B-4F88-8221-BDE140EDD1EA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
